--- a/Informes/Informe_Palestino_vs_O'sommer_2026-09-08.xlsx
+++ b/Informes/Informe_Palestino_vs_O'sommer_2026-09-08.xlsx
@@ -5271,28 +5271,28 @@
         </is>
       </c>
       <c r="B26" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D26" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F26" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="B27" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C27" s="11" t="n">
         <v>0</v>
@@ -5314,16 +5314,16 @@
         <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="B28" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D28" s="11" t="n">
         <v>0</v>
@@ -5345,16 +5345,16 @@
         <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H28" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="B29" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D29" s="11" t="n">
         <v>0</v>
@@ -5379,13 +5379,13 @@
         <v>0</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H29" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
@@ -5401,7 +5401,7 @@
         <v>0</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E30" s="11" t="n">
         <v>0</v>
@@ -5410,13 +5410,13 @@
         <v>0</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H30" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -5432,7 +5432,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E31" s="11" t="n">
         <v>0</v>
@@ -5441,13 +5441,13 @@
         <v>0</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H31" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -5463,7 +5463,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E32" s="11" t="n">
         <v>0</v>
@@ -5472,13 +5472,13 @@
         <v>0</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H32" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -5491,10 +5491,10 @@
         <v>0</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" s="11" t="n">
         <v>0</v>
@@ -5503,13 +5503,13 @@
         <v>0</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -5522,7 +5522,7 @@
         <v>0</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" s="11" t="n">
         <v>0</v>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -5550,28 +5550,28 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H35" s="13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I35" s="13" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36"/>
